--- a/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
+++ b/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="143">
   <si>
     <t xml:space="preserve">Kapitalbehov og finansiering: oppgaver til kapittel 6</t>
   </si>
@@ -65,7 +65,13 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hører hjemme</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Fjell Elektro ved oppstart: holder 800 000 kr?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hører ikke hjemme</t>
   </si>
   <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
@@ -250,7 +256,16 @@
     <t xml:space="preserve">f) To setninger til Kari: hvilken knapp bør hun skru på først, dagene hos kundene eller dagene på lager, og hva gjør hun konkret?</t>
   </si>
   <si>
+    <t xml:space="preserve">Greit: kassekreditten er billigere enn banklånet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Fjells finansieringsplan, og hva lånet egentlig koster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei: utstyret skal vare i mange år og må finansieres med egenkapital og langsiktig lån</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greit, så lenge rammen er stor nok</t>
   </si>
   <si>
     <t xml:space="preserve">Kapitalbehovet for Fjell er 1 019 479 kr (oppgave 1A). Eieren har 300 000 kr i aksjekapital og 500 000 kr i banklån: et serielån over fem år til 7,5 % rente, avregnet hver måned. Grossisten gir 30 dagers kreditt. Banken krever minst 30 % egenkapital og at det langsiktige er finansiert langsiktig. Går planen opp, og hva sier dere til banken?</t>
@@ -638,7 +653,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -661,6 +676,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1123,7 +1142,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G44"/>
+  <dimension ref="B1:Z44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1131,366 +1150,407 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="B11" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="C11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="13" t="n">
         <v>300000</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="13"/>
+      <c r="B13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="13"/>
+      <c r="B14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="13" t="n">
         <v>150000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="13"/>
+      <c r="B16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
-        <v>36</v>
+      <c r="B21" s="15" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="15" t="str">
+        <v>39</v>
+      </c>
+      <c r="C22" s="16" t="str">
         <f aca="false">IF(D13="","Skriv svaret i cellen D13.",IF(ABS(D13-(1400000*18/360))&lt;=1,"Riktig.",IF(ABS(D13-(1400000*1.25*18/360))&lt;=1,"Du har tatt med merverdiavgift. Varelageret regnes uten: den inngående avgiften får bedriften tilbake.",IF(ABS(D13-(1400000*30/360))&lt;=1,"Du har brukt 30 dager. Materiellet ligger 18 dager på lager; 30 er kundenes kredittid.",IF(ABS(D13-(1400000/18))&lt;=1,"Du har delt på dagene. Gang med dagene på lager, og del på 360.","Ikke riktig ennå. Varelager er materiellforbruket uten merverdiavgift ganger dager på lager, delt på 360.")))))</f>
         <v>Skriv svaret i cellen D13.</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="15" t="str">
+        <v>40</v>
+      </c>
+      <c r="C23" s="16" t="str">
         <f aca="false">IF(D14="","Skriv svaret i cellen D14.",IF(ABS(D14-(4795000*1.25*30/360))&lt;=1,"Riktig.",IF(ABS(D14-(4795000*30/360))&lt;=1,"Du har regnet uten merverdiavgift. Kunden skylder hele fakturaen, med avgift: gang salget med 1,25 først.",IF(ABS(D14-(4795000*1.25*18/360))&lt;=1,"Du har brukt 18 dager. Kundene får 30 dagers kredittid; 18 er dagene på lager.",IF(ABS(D14-(4795000*1.25/30))&lt;=1,"Du har delt på dagene. Gang med kredittiden, og del på 360.","Ikke riktig ennå. Kundefordringer er salget med merverdiavgift ganger kredittiden, delt på 360.")))))</f>
         <v>Skriv svaret i cellen D14.</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="15" t="str">
+        <v>41</v>
+      </c>
+      <c r="C24" s="16" t="str">
         <f aca="false">IF(D16="","Skriv svaret i cellen D16.",IF(ABS(D16-(300000+ROUND(1400000*18/360,0)+ROUND(4795000*1.25*30/360,0)+150000))&lt;=2,"Riktig.",IF(ABS(D16-(300000+ROUND(1400000*18/360,0)+ROUND(4795000*1.25*30/360,0)))&lt;=2,"Du har glemt likviditetsreserven, 150 000. Pengene du holder av, er også kapital som må skaffes.",IF(ABS(D16-(300000+144000+ROUND(1400000*18/360,0)+ROUND(4795000*1.25*30/360,0)+150000))&lt;=2,"Du har tatt med leasingen av bilene. Leasede biler kjøpes ikke og binder ingen kapital; leia er en driftskostnad.",IF(ABS(D16-(ROUND(1400000*18/360,0)+ROUND(4795000*1.25*30/360,0)+150000))&lt;=2,"Du har glemt utstyret, 300 000. Investeringen er den første posten i kapitalbehovet.",IF(ABS(D16-(300000+ROUND(1400000*18/360,0)+ROUND(4795000*1.25*30/360,0)+150000+500000))&lt;=2,"Du har lagt til banklånet. Lånet er finansieringen, ikke behovet: det står på den andre siden av balansen.","Ikke riktig ennå. Legg sammen utstyr, varelager, kundefordringer og reserve. Ikke leasing, ikke lånet."))))))</f>
         <v>Skriv svaret i cellen D16.</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="B26" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="G27" s="19" t="str">
+      <c r="B27" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="G27" s="20" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Hører hjemme","Riktig. Investering i anleggsmidler (avsnitt 6.1.1).","Ikke riktig. Investering i anleggsmidler (avsnitt 6.1.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="G28" s="19" t="str">
+      <c r="B28" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="G28" s="20" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Hører ikke hjemme","Riktig. Leies, ikke eies. Ingen kjøpesum; leia er en driftskostnad hver måned (6.9).","Ikke riktig. Leies, ikke eies. Ingen kjøpesum; leia er en driftskostnad hver måned (6.9)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="G29" s="19" t="str">
+      <c r="B29" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="G29" s="20" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Hører hjemme","Riktig. Varelager, regnet uten merverdiavgift (6.1.2).","Ikke riktig. Varelager, regnet uten merverdiavgift (6.1.2)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="G30" s="19" t="str">
+      <c r="B30" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="G30" s="20" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Hører hjemme","Riktig. Kundefordringer, regnet med merverdiavgift (6.1.3).","Ikke riktig. Kundefordringer, regnet med merverdiavgift (6.1.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="G31" s="19" t="str">
+      <c r="B31" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="G31" s="20" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Hører hjemme","Riktig. Buffer mot uforutsette utlegg (6.1.4). Står som bankinnskudd i balansen.","Ikke riktig. Buffer mot uforutsette utlegg (6.1.4). Står som bankinnskudd i balansen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="G32" s="19" t="str">
+      <c r="B32" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="G32" s="20" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Hører ikke hjemme","Riktig. Finansiering. Lånet dekker behovet; det står på den andre siden av balansen.","Ikke riktig. Finansiering. Lånet dekker behovet; det står på den andre siden av balansen."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G34" s="19" t="str">
+      <c r="B34" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="20" t="str">
         <f aca="false">IF(C34="","Skriv svaret i den gule cellen.",IF(ABS(C34-(300000+ROUND(1400000*18/360,0)+ROUND(4795000*1.25*60/360,0)+150000))&lt;=2,"Riktig.",IF(ABS(C34-(300000+ROUND(1400000*18/360,0)+ROUND(4795000*1.25*30/360,0)+150000))&lt;=2,"Det er svaret i c, med 30 dager. Nå er kredittiden 60 dager: kundefordringene dobles.",IF(ABS(C34-(ROUND(4795000*1.25*60/360,0)))&lt;=2,"Det er bare kundefordringene ved 60 dager. Oppgaven spør om hele kapitalbehovet.",IF(ABS(C34-(300000+ROUND(1400000*60/360,0)+ROUND(4795000*1.25*60/360,0)+150000))&lt;=2,"Du har satt lageret til 60 dager også. Det er bare kundenes kredittid som endres; lageret er fortsatt 18 dager.","Ikke riktig ennå. Kundefordringene ved 60 dager er 5 993 750 × 60 / 360. Resten av postene er som i c.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="22" t="str">
+      <c r="B40" s="23" t="str">
         <f aca="false">IF(LEN(B37)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kundefordring",B37)),ISNUMBER(SEARCH("019",B37))),"Bra: du bruker kapitalbehovet og peker på kundefordringene. Si gjerne også hvor mye som mangler (1 019 479 − 800 000 = 219 479 kr).",IF(OR(ISNUMBER(SEARCH("kundefordring",B37)),ISNUMBER(SEARCH("019",B37))),"Du er på sporet. Ta med både tallet for kapitalbehovet (1 019 479 kr) og hva som er den store posten han glemte: kundefordringene.","Tips: kapitalbehovet er 1 019 479 kr, ikke 300 000. Det han glemte, er ventetiden: materiellet på lager (70 000) og fakturaene kundene ikke har betalt (499 479). Det mangler 219 479 kr.")))</f>
         <v/>
       </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="18"/>
+      <c r="B41" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="24" t="str">
+      <c r="B42" s="25" t="str">
         <f aca="false">IF(C41="JA","Hint: Varelager: 1 400 000 × 18 / 360 = 70 000. Kundefordringer: 4 795 000 × 1,25 = 5 993 750, × 30 / 360 = 499 479. Sum: 300 000 + 70 000 + 499 479 + 150 000 = 1 019 479. Ved 60 dager: kundefordringer 998 958, sum 1 518 958.","")</f>
         <v/>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
+      <c r="B44" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -1596,27 +1656,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Hører hjemme,Hører ikke hjemme"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Hører hjemme,Hører ikke hjemme"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Hører hjemme,Hører ikke hjemme"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Hører hjemme,Hører ikke hjemme"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Hører hjemme,Hører ikke hjemme"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Hører hjemme,Hører ikke hjemme"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C41" type="list">
@@ -1651,7 +1711,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1660,280 +1720,280 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>23</v>
+      <c r="B11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>1400000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>4200000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>8390000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="25" t="n">
+      <c r="B15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <f aca="false">22400000*1.25</f>
         <v>28000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="19" t="str">
+      <c r="B21" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="20" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(1400000/8390000*360,0)))&lt;=1,"Riktig.",IF(ABS(C21-(ROUND(8390000/1400000,0)))&lt;=1,"Du har regnet omløpshastigheten, antall ganger lageret byttes ut i året. Dagene er 360 delt på den: 360 / 6 = 60.",IF(ABS(C21-(ROUND(1400000/8390000*365,0)))&lt;=1,"Du har brukt 365 dager. Boka regner året som 360 dager, 12 måneder à 30.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="19" t="str">
+      <c r="B22" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="20" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(ABS(C22-(ROUND(4200000/28000000*360,0)))&lt;=1,"Riktig.",IF(ABS(C22-(ROUND(4200000/22400000*360,0)))&lt;=1,"Du har brukt salget uten merverdiavgift. Kunden skylder fakturaen med avgift, så salget må være 28 000 000.",IF(ABS(C22-(ROUND(28000000/4200000,0)))&lt;=1,"Du har regnet hvor mange ganger i året kundefordringene byttes ut. Dagene er 360 delt på det.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="19" t="str">
+      <c r="B23" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="20" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(ABS(C23-(ROUND(28000000/360,0)))&lt;=2,"Riktig.",IF(ABS(C23-(ROUND(22400000/360,0)))&lt;=2,"Du har brukt salget uten merverdiavgift. Kundefordringene er med avgift: 28 000 000 / 360.",IF(ABS(C23-(ROUND(4200000/360,0)))&lt;=2,"Du har delt kundefordringene på 360. Én dag er årets salg delt på 360, ikke beholdningen.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="19" t="str">
+      <c r="B24" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="20" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(8390000/360,0)))&lt;=2,"Riktig.",IF(ABS(C24-(ROUND(8390000*1.25/360,0)))&lt;=2,"Du har lagt til merverdiavgift. Lageret regnes uten: den inngående avgiften får Nordlys tilbake.",IF(ABS(C24-(ROUND(1400000/360,0)))&lt;=2,"Du har delt varelageret på 360. Én dag er årets varekostnad delt på 360.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="19" t="str">
+      <c r="B25" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="20" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(ABS(C25-(ROUND(28000000*10/360,0)))&lt;=5,"Riktig.",IF(ABS(C25-(ROUND(22400000*10/360,0)))&lt;=5,"Du har brukt salget uten merverdiavgift. Bruk 28 000 000.",IF(ABS(C25-(ROUND(28000000/360,0)))&lt;=5,"Det er én dag. Oppgaven spør om ti dager: gang med 10.","Ikke riktig ennå. Ti ganger svaret i c. Sammenlikn med kassekreditten på 300 000."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="B27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22" t="str">
+      <c r="B31" s="23" t="str">
         <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Bra: du peker på kundene og sier hva hun gjør med fakturaene. Én dag hos kundene er verdt mer enn tre dager på lager, og ti dager frigjør mer enn hele kassekreditten.",IF(OR(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Du er på sporet. Si både hvilken knapp (kundene, fordi én dag der er verdt 77 778 kr mot 23 306 på lager) og hva hun konkret gjør: fakturere samme dag som jobben er ferdig, kortere frist der hun kan, og følge opp forfall.","Tips: én dag hos kundene flytter 77 778 kr, én dag på lager 23 306 kr. Kundene først. Konkret: fakturer samme dag som jobben er ferdig, avtal kortere frist med små kunder, følg opp forfall. Ti dager frigjør 777 778 kr, mer enn kassekreditten på 300 000.")))</f>
         <v/>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="18"/>
+      <c r="B32" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="24" t="str">
+      <c r="B33" s="25" t="str">
         <f aca="false">IF(C32="JA","Hint: a: 1 400 000 / 8 390 000 × 360 = 60 dager. b: 4 200 000 / 28 000 000 × 360 = 54 dager. c: 28 000 000 / 360 = 77 778. d: 8 390 000 / 360 = 23 306. e: 77 778 × 10 = 777 778, mer enn kassekreditten på 300 000.","")</f>
         <v/>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="B35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2014,7 +2074,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B1:Z39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2022,321 +2082,333 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>23</v>
+      <c r="B11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="13" t="n">
         <v>1019479</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="13" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="13" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="13"/>
+      <c r="B15" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="13"/>
+      <c r="B16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="19" t="str">
+      <c r="B21" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="20" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(300000/1019479*100,1)))&lt;=0.1,"Riktig.",IF(ABS(C21-(ROUND(300000/300000*100,1)))&lt;=0.1,"Du har delt på utstyret. Egenkapitalkravet regnes av hele kapitalbehovet, 1 019 479.",IF(ABS(C21-(ROUND(300000/800000*100,1)))&lt;=0.1,"Du har delt på egenkapital pluss lån. Andelen er egenkapitalen delt på kapitalbehovet.",IF(ABS(C21-(ROUND(300000/1019479,1)))&lt;=0.1,"Du har svart som brøk. Gang med 100 og svar i prosent, for eksempel 25,0.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
-        <v>36</v>
+      <c r="B22" s="15" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="15" t="str">
+        <v>95</v>
+      </c>
+      <c r="C23" s="16" t="str">
         <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(ABS(D15-(ROUND(1750000*30/360,0)))&lt;=1,"Riktig.",IF(ABS(D15-(ROUND(1400000*30/360,0)))&lt;=1,"Du har regnet uten merverdiavgift. Leverandørgjelden er med avgift, som kundefordringene: grossisten skal ha hele fakturaen.",IF(ABS(D15-(ROUND(1750000*18/360,0)))&lt;=1,"Du har brukt 18 dager. Grossisten gir 30 dagers kreditt; 18 er dagene på lager.","Ikke riktig ennå. Leverandørgjeld er varekjøpet med merverdiavgift ganger kredittiden, delt på 360."))))</f>
         <v>Skriv svaret i cellen D15.</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" s="15" t="str">
+        <v>96</v>
+      </c>
+      <c r="C24" s="16" t="str">
         <f aca="false">IF(D16="","Skriv svaret i cellen D16.",IF(ABS(D16-(1019479-300000-500000-ROUND(1750000*30/360,0)))&lt;=2,"Riktig.",IF(ABS(D16-(1019479-300000-500000))&lt;=2,"Du har glemt å trekke fra leverandørgjelden. Grossisten finansierer 145 833 av behovet.",IF(ABS(D16-(1019479-300000-ROUND(1750000*30/360,0)))&lt;=2,"Du har glemt banklånet, 500 000. Det dekker en del av behovet.",IF(ABS(D16-(1019479-800000-2*ROUND(1750000*30/360,0)))&lt;=2,"Du har trukket fra leverandørgjelden to ganger. Den trekkes fra én gang.","Ikke riktig ennå. Trekk egenkapital, banklån og leverandørgjeld fra kapitalbehovet. Det som er igjen, er annen kortsiktig gjeld.")))))</f>
         <v>Skriv svaret i cellen D16.</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G26" s="19" t="str">
+      <c r="B26" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="20" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(ABS(C26-(100000+500000*0.075))&lt;=1,"Riktig.",IF(ABS(C26-(500000*0.075))&lt;=1,"Det er bare renten. Terminbeløpet er avdrag pluss rente.",IF(ABS(C26-(100000))&lt;=1,"Det er bare avdraget. Legg til renten på hele lånet det første året.",IF(ABS(C26-(100000+400000*0.075))&lt;=1,"Du har regnet rente av 400 000. Det første året er hele lånet, 500 000, utestående.",IF(ABS(C26-(500000*0.075/12))&lt;=1,"Du har regnet én måneds rente. Oppgaven spør om hele året.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="19" t="str">
+      <c r="B27" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="29"/>
+      <c r="D27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" s="20" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(ROUND(((1+0.075/12)^12-1)*100,2)))&lt;=0.01,"Riktig.",IF(ABS(C27-(7.5))&lt;=0.01,"Det er den nominelle renten. Med månedlig avregning blir den effektive høyere: (1 + 0,075 / 12)^12 − 1.",IF(ABS(C27-(ROUND(((1+0.075/12)^12-1),2)))&lt;=0.01,"Du har svart som brøk. Gang med 100 og svar i prosent.",IF(ABS(C27-(ROUND(((1+0.075/4)^4-1)*100,2)))&lt;=0.01,"Du har brukt fire avregninger i året. Renten avregnes hver måned: tolv ganger.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="G29" s="19" t="str">
+      <c r="B29" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="G29" s="20" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Nei: utstyret skal vare i mange år og må finansieres med egenkapital og langsiktig lån","Riktig. Anleggsmidler finansieres langsiktig (avsnitt 6.2). Kassekreditten skal tilbake fortløpende og koster provisjon på rammen pluss rente på det som er trukket (6.8).","Ikke riktig. Anleggsmidler finansieres langsiktig (avsnitt 6.2). Kassekreditten skal tilbake fortløpende og koster provisjon på rammen pluss rente på det som er trukket (6.8)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="22" t="str">
+      <c r="B35" s="23" t="str">
         <f aca="false">IF(LEN(B32)&lt;40,"",IF(AND(ISNUMBER(SEARCH("langsiktig",B32)),ISNUMBER(SEARCH("egenkapital",B32))),"Bra: du bruker både kravet til langsiktig kapital og egenkapitalandelen. Si gjerne også at de 73 646 kronene må være en avtalt kassekreditt, og hva dere gjør ved 60 dager.",IF(OR(ISNUMBER(SEARCH("langsiktig",B32)),ISNUMBER(SEARCH("egenkapital",B32))),"Du er på sporet. Ta med begge: langsiktig kapital 800 000 dekker kravet på 335 000, og egenkapitalen er 29,4 %, like under 30. Og ved 60 dager: skyte inn mer, korte ned dagene, eller faktoring.","Tips: egenkapital + lån = 800 000 dekker kravet (300 000 + 70 000 / 2 = 335 000) med god margin. Egenkapitalen er 29,4 %; 5 844 kr til gir 30 %. De 73 646 må være en avtalt kassekreditt. Ved 60 dager faller andelen til 19,8 %: skyt inn mer, kort ned dagene, eller vurder faktoring.")))</f>
         <v/>
       </c>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="18"/>
+      <c r="B36" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="24" t="str">
+      <c r="B37" s="25" t="str">
         <f aca="false">IF(C36="JA","Hint: a: 300 000 / 1 019 479 = 29,4 %. b: 1 750 000 × 30 / 360 = 145 833. c: 1 019 479 − 300 000 − 500 000 − 145 833 = 73 646. d: 100 000 + 37 500 = 137 500. e: 1,00625 opphøyd i 12 er 1,0776; minus 1 gir 7,76 %.","")</f>
         <v/>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="B39" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2408,7 +2480,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Greit: kassekreditten er billigere enn banklånet,Nei: utstyret skal vare i mange år og må finansieres med egenkapital og langsiktig lån,Greit,så lenge rammen er stor nok"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
@@ -2441,221 +2513,221 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="29" t="s">
-        <v>96</v>
+      <c r="B2" s="30" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>77</v>
+      <c r="B5" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="25" t="n">
+      <c r="B6" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="26" t="n">
         <v>70000</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>101</v>
+      <c r="D6" s="32" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="25" t="n">
+      <c r="B7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="26" t="n">
         <v>499479</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>103</v>
+      <c r="D7" s="32" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="25" t="n">
+      <c r="B8" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="26" t="n">
         <v>1019479</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>105</v>
+      <c r="D8" s="32" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="31" t="s">
-        <v>107</v>
+      <c r="B9" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="26"/>
+      <c r="D9" s="32" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="25" t="n">
+      <c r="B10" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="26" t="n">
         <v>1518958</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>109</v>
+      <c r="D10" s="32" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="31" t="s">
-        <v>111</v>
+      <c r="B11" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="32" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="25" t="n">
+      <c r="B12" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="26" t="n">
         <v>60</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>113</v>
+      <c r="D12" s="32" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="25" t="n">
+      <c r="B13" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>115</v>
+      <c r="D13" s="32" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C14" s="25" t="n">
+      <c r="B14" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="26" t="n">
         <v>77778</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>117</v>
+      <c r="D14" s="32" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="25" t="n">
+      <c r="B15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <v>23306</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>119</v>
+      <c r="D15" s="32" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="25" t="n">
+      <c r="B16" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="26" t="n">
         <v>777778</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>121</v>
+      <c r="D16" s="32" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="31" t="s">
-        <v>123</v>
+      <c r="B17" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="26"/>
+      <c r="D17" s="32" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="31" t="s">
-        <v>125</v>
+      <c r="B18" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="32" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" s="25" t="n">
+      <c r="B19" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="26" t="n">
         <v>145833</v>
       </c>
-      <c r="D19" s="31" t="s">
-        <v>127</v>
+      <c r="D19" s="32" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C20" s="25" t="n">
+      <c r="B20" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="26" t="n">
         <v>73646</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>129</v>
+      <c r="D20" s="32" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="25" t="n">
+      <c r="B21" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="26" t="n">
         <v>137500</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>131</v>
+      <c r="D21" s="32" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="31" t="s">
-        <v>133</v>
+      <c r="B22" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="32" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="31" t="s">
-        <v>135</v>
+      <c r="B23" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="26"/>
+      <c r="D23" s="32" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="31" t="s">
-        <v>137</v>
+      <c r="B24" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="32" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
+++ b/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
@@ -204,7 +204,7 @@
     <t xml:space="preserve">Tallene fra regnskapet 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Balansen per 31.12.2026: varelager 1 400 000 kr, kundefordringer 4 200 000 kr, kassekreditt 300 000 kr. Resultatregnskapet 2026: salgsinntekt 22 400 000 kr uten merverdiavgift (28 000 000 kr med), varekostnad 8 390 000 kr. Bransjen (NHO Elektro, lønnsomhetsrapport 2025): kredittid kunder 54 dager, lager 57 dager. Året er 360 dager.</t>
+    <t xml:space="preserve">Balansen per 31.12.2026: varelager 1 400 000 kr, kundefordringer 4 200 000 kr, kassekreditt 300 000 kr. Resultatregnskapet 2026: salgsinntekt 22 400 000 kr uten merverdiavgift (28 000 000 kr med), materialkostnad 7 990 000 kr (varekostnaden på 7 990 000 inneholder også 400 000 i innleide montører, som aldri ligger på lager). Bransjen (NHO Elektro, lønnsomhetsrapport 2025): kredittid kunder 54 dager, lager 57 dager. Året er 360 dager.</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys per 31.12.2026</t>
@@ -216,7 +216,7 @@
     <t xml:space="preserve">Kundefordringer</t>
   </si>
   <si>
-    <t xml:space="preserve">Varekostnad 2026</t>
+    <t xml:space="preserve">Materialkostnad 2026 (varekostnad uten innleie)</t>
   </si>
   <si>
     <t xml:space="preserve">Salg 2026 med merverdiavgift (22 400 000 × 1,25)</t>
@@ -225,14 +225,14 @@
     <t xml:space="preserve">Kassekreditt</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Snu formelen for varelageret: dager på lager = varelager / varekostnad × 360. Hele dager.
+    <t xml:space="preserve">1. Snu formelen for varelageret: dager på lager = varelager / materialkostnad × 360. Hele dager.
 2. Snu formelen for kundefordringene: kredittid = kundefordringer / salg med merverdiavgift × 360. Hele dager.
 3. Regn hva én dag flytter: årsbeløpet delt på 360. Hele kroner.
 4. Regn hvor mye Kari frigjør hvis kundene betaler ti dager tidligere, og sammenlikn med kassekreditten.
 5. Skriv to setninger til Kari i f.</t>
   </si>
   <si>
-    <t xml:space="preserve">a) Dager på lager: 1 400 000 / 8 390 000 × 360, hele dager</t>
+    <t xml:space="preserve">a) Dager på lager: 1 400 000 / 7 990 000 × 360, hele dager</t>
   </si>
   <si>
     <t xml:space="preserve">dager</t>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">kr per dag</t>
   </si>
   <si>
-    <t xml:space="preserve">d) Én dag på lager flytter: 8 390 000 / 360, hele kroner</t>
+    <t xml:space="preserve">d) Én dag på lager flytter: 7 990 000 / 360, hele kroner</t>
   </si>
   <si>
     <t xml:space="preserve">e) Kundene betaler ti dager tidligere. Hvor mye frigjøres? 28 000 000 × 10 / 360, hele kroner</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">1B a) Dager på lager</t>
   </si>
   <si>
-    <t xml:space="preserve">1 400 000 / 8 390 000 × 360 = 60 dager (bransjen: 57)</t>
+    <t xml:space="preserve">1 400 000 / 7 990 000 × 360 = 63 dager (bransjen: 57)</t>
   </si>
   <si>
     <t xml:space="preserve">1B b) Kredittid kunder</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">1B d) Én dag på lager</t>
   </si>
   <si>
-    <t xml:space="preserve">8 390 000 / 360 = 23 306 kr</t>
+    <t xml:space="preserve">7 990 000 / 360 = 22 194 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1B e) Ti dager tidligere</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1B f) Til Kari</t>
   </si>
   <si>
-    <t xml:space="preserve">Kundene først: én dag der er verdt 77 778 kr mot 23 306 på lager. Fakturer samme dag som jobben er ferdig, avtal kortere frist der hun kan, følg opp forfall. Det koster ingen rente</t>
+    <t xml:space="preserve">Kundene først: én dag der er verdt 77 778 kr mot 22 194 på lager. Fakturer samme dag som jobben er ferdig, avtal kortere frist der hun kan, følg opp forfall. Det koster ingen rente</t>
   </si>
   <si>
     <t xml:space="preserve">1C a) Egenkapitalandel</t>
@@ -1779,7 +1779,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>58</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>8390000</v>
+        <v>7990000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1867,7 +1867,7 @@
         <v>67</v>
       </c>
       <c r="G21" s="20" t="str">
-        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(1400000/8390000*360,0)))&lt;=1,"Riktig.",IF(ABS(C21-(ROUND(8390000/1400000,0)))&lt;=1,"Du har regnet omløpshastigheten, antall ganger lageret byttes ut i året. Dagene er 360 delt på den: 360 / 6 = 60.",IF(ABS(C21-(ROUND(1400000/8390000*365,0)))&lt;=1,"Du har brukt 365 dager. Boka regner året som 360 dager, 12 måneder à 30.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(1400000/7990000*360,0)))&lt;=1,"Riktig.",IF(ABS(C21-(ROUND(7990000/1400000,0)))&lt;=1,"Du har regnet omløpshastigheten, antall ganger lageret byttes ut i året. Dagene er 360 delt på den: 360 / 5,7 = 63.",IF(ABS(C21-(ROUND(1400000/7990000*365,0)))&lt;=1,"Du har brukt 365 dager. Boka regner året som 360 dager, 12 måneder à 30.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>70</v>
       </c>
       <c r="G24" s="20" t="str">
-        <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(8390000/360,0)))&lt;=2,"Riktig.",IF(ABS(C24-(ROUND(8390000*1.25/360,0)))&lt;=2,"Du har lagt til merverdiavgift. Lageret regnes uten: den inngående avgiften får Nordlys tilbake.",IF(ABS(C24-(ROUND(1400000/360,0)))&lt;=2,"Du har delt varelageret på 360. Én dag er årets varekostnad delt på 360.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(7990000/360,0)))&lt;=2,"Riktig.",IF(ABS(C24-(ROUND(7990000*1.25/360,0)))&lt;=2,"Du har lagt til merverdiavgift. Lageret regnes uten: den inngående avgiften får Nordlys tilbake.",IF(ABS(C24-(ROUND(1400000/360,0)))&lt;=2,"Du har delt varelageret på 360. Én dag er årets materialkostnad delt på 360.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="str">
-        <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Bra: du peker på kundene og sier hva hun gjør med fakturaene. Én dag hos kundene er verdt mer enn tre dager på lager, og ti dager frigjør mer enn hele kassekreditten.",IF(OR(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Du er på sporet. Si både hvilken knapp (kundene, fordi én dag der er verdt 77 778 kr mot 23 306 på lager) og hva hun konkret gjør: fakturere samme dag som jobben er ferdig, kortere frist der hun kan, og følge opp forfall.","Tips: én dag hos kundene flytter 77 778 kr, én dag på lager 23 306 kr. Kundene først. Konkret: fakturer samme dag som jobben er ferdig, avtal kortere frist med små kunder, følg opp forfall. Ti dager frigjør 777 778 kr, mer enn kassekreditten på 300 000.")))</f>
+        <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Bra: du peker på kundene og sier hva hun gjør med fakturaene. Én dag hos kundene er verdt mer enn tre dager på lager, og ti dager frigjør mer enn hele kassekreditten.",IF(OR(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Du er på sporet. Si både hvilken knapp (kundene, fordi én dag der er verdt 77 778 kr mot 22 194 på lager) og hva hun konkret gjør: fakturere samme dag som jobben er ferdig, kortere frist der hun kan, og følge opp forfall.","Tips: én dag hos kundene flytter 77 778 kr, én dag på lager 22 194 kr. Kundene først. Konkret: fakturer samme dag som jobben er ferdig, avtal kortere frist med små kunder, følg opp forfall. Ti dager frigjør 777 778 kr, mer enn kassekreditten på 300 000.")))</f>
         <v/>
       </c>
       <c r="C31" s="23"/>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="25" t="str">
-        <f aca="false">IF(C32="JA","Hint: a: 1 400 000 / 8 390 000 × 360 = 60 dager. b: 4 200 000 / 28 000 000 × 360 = 54 dager. c: 28 000 000 / 360 = 77 778. d: 8 390 000 / 360 = 23 306. e: 77 778 × 10 = 777 778, mer enn kassekreditten på 300 000.","")</f>
+        <f aca="false">IF(C32="JA","Hint: a: 1 400 000 / 7 990 000 × 360 = 63 dager. b: 4 200 000 / 28 000 000 × 360 = 54 dager. c: 28 000 000 / 360 = 77 778. d: 7 990 000 / 360 = 22 194. e: 77 778 × 10 = 777 778, mer enn kassekreditten på 300 000.","")</f>
         <v/>
       </c>
       <c r="C33" s="25"/>
@@ -2602,7 +2602,7 @@
         <v>117</v>
       </c>
       <c r="C12" s="26" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>118</v>
@@ -2635,7 +2635,7 @@
         <v>123</v>
       </c>
       <c r="C15" s="26" t="n">
-        <v>23306</v>
+        <v>22194</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>124</v>

--- a/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
+++ b/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
@@ -653,7 +653,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -784,6 +784,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="right" vertical="center" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1071,7 +1079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1096,27 +1104,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1295,8 +1303,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="33" r="B13" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="13" t="s">
@@ -1304,8 +1312,8 @@
       </c>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="33" r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="13" t="s">
@@ -1343,7 +1351,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>37</v>
       </c>
@@ -1848,7 +1856,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>65</v>
       </c>
@@ -2187,11 +2195,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c s="34" r="C12" t="s">
         <v>84</v>
       </c>
       <c r="D12" s="13" t="n">
@@ -2220,8 +2228,8 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="33" r="B15" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="13" t="s">
@@ -2248,7 +2256,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="90" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>92</v>
       </c>
@@ -2328,7 +2336,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
         <v>99</v>
       </c>

--- a/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
+++ b/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Oppgaver_v6.xlsx
@@ -416,7 +416,7 @@
     <t xml:space="preserve">1B e) Ti dager tidligere</t>
   </si>
   <si>
-    <t xml:space="preserve">28 000 000 × 10 / 360 = 777 778 kr, mer enn kassekreditten på 300 000</t>
+    <t xml:space="preserve">28 000 000 × 10 / 360 = 777 778 kr, mer enn de 300 000 kr som er trukket på kassekreditten</t>
   </si>
   <si>
     <t xml:space="preserve">1B f) Til Kari</t>
@@ -653,7 +653,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -784,14 +784,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment wrapText="true" horizontal="right" vertical="center" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1104,27 +1096,27 @@
         <v>6</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1303,8 +1295,8 @@
         <v>15</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="33" r="B13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="12" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="13" t="s">
@@ -1312,8 +1304,8 @@
       </c>
       <c r="D13" s="14"/>
     </row>
-    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="33" r="B14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="13" t="s">
@@ -1351,7 +1343,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row ht="75.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>37</v>
       </c>
@@ -1856,7 +1848,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row ht="75.75" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>65</v>
       </c>
@@ -1967,7 +1959,7 @@
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="str">
-        <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Bra: du peker på kundene og sier hva hun gjør med fakturaene. Én dag hos kundene er verdt mer enn tre dager på lager, og ti dager frigjør mer enn hele kassekreditten.",IF(OR(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Du er på sporet. Si både hvilken knapp (kundene, fordi én dag der er verdt 77 778 kr mot 22 194 på lager) og hva hun konkret gjør: fakturere samme dag som jobben er ferdig, kortere frist der hun kan, og følge opp forfall.","Tips: én dag hos kundene flytter 77 778 kr, én dag på lager 22 194 kr. Kundene først. Konkret: fakturer samme dag som jobben er ferdig, avtal kortere frist med små kunder, følg opp forfall. Ti dager frigjør 777 778 kr, mer enn kassekreditten på 300 000.")))</f>
+        <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Bra: du peker på kundene og sier hva hun gjør med fakturaene. Én dag hos kundene er verdt mer enn tre dager på lager, og ti dager frigjør mer enn det som er trukket på kassekreditten.",IF(OR(ISNUMBER(SEARCH("kunde",B28)),ISNUMBER(SEARCH("faktur",B28))),"Du er på sporet. Si både hvilken knapp (kundene, fordi én dag der er verdt 77 778 kr mot 22 194 på lager) og hva hun konkret gjør: fakturere samme dag som jobben er ferdig, kortere frist der hun kan, og følge opp forfall.","Tips: én dag hos kundene flytter 77 778 kr, én dag på lager 22 194 kr. Kundene først. Konkret: fakturer samme dag som jobben er ferdig, avtal kortere frist med små kunder, følg opp forfall. Ti dager frigjør 777 778 kr, mer enn de 300 000 kr som er trukket på kassekreditten.")))</f>
         <v/>
       </c>
       <c r="C31" s="23"/>
@@ -1982,9 +1974,9 @@
       </c>
       <c r="C32" s="19"/>
     </row>
-    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="25" t="str">
-        <f aca="false">IF(C32="JA","Hint: a: 1 400 000 / 7 990 000 × 360 = 63 dager. b: 4 200 000 / 28 000 000 × 360 = 54 dager. c: 28 000 000 / 360 = 77 778. d: 7 990 000 / 360 = 22 194. e: 77 778 × 10 = 777 778, mer enn kassekreditten på 300 000.","")</f>
+        <f aca="false">IF(C32="JA","Hint: a: 1 400 000 / 7 990 000 × 360 = 63 dager. b: 4 200 000 / 28 000 000 × 360 = 54 dager. c: 28 000 000 / 360 = 77 778. d: 7 990 000 / 360 = 22 194. e: 77 778 × 10 = 777 778, mer enn de 300 000 kr som er trukket på kassekreditten.","")</f>
         <v/>
       </c>
       <c r="C33" s="25"/>
@@ -2195,11 +2187,11 @@
         <v>25</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
         <v>83</v>
       </c>
-      <c s="34" r="C12" t="s">
+      <c r="C12" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D12" s="13" t="n">
@@ -2228,8 +2220,8 @@
         <v>500000</v>
       </c>
     </row>
-    <row ht="31.5" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c s="33" r="B15" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="13" t="s">
@@ -2256,7 +2248,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row ht="90" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
         <v>92</v>
       </c>
@@ -2336,7 +2328,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row ht="46.5" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="18" t="s">
         <v>99</v>
       </c>
